--- a/DATA/bd-subnacionales.xlsx
+++ b/DATA/bd-subnacionales.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29407"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebasteitor\Desktop\MODELOS ECONOMETRICOS\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE34AAF2-FDF6-4B94-A6C4-61D1A1258588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19EABEDC-5E04-4357-9325-4E322245E77A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{7DE3D96D-6A87-41CE-8431-31A34F3BDAB7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7DE3D96D-6A87-41CE-8431-31A34F3BDAB7}"/>
   </bookViews>
   <sheets>
     <sheet name="bdsub" sheetId="1" r:id="rId1"/>
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>PIM</t>
   </si>
@@ -176,6 +176,114 @@
   </si>
   <si>
     <t>PBILIMA</t>
+  </si>
+  <si>
+    <t>2016Q1</t>
+  </si>
+  <si>
+    <t>2016Q2</t>
+  </si>
+  <si>
+    <t>2016Q3</t>
+  </si>
+  <si>
+    <t>2016Q4</t>
+  </si>
+  <si>
+    <t>2017Q1</t>
+  </si>
+  <si>
+    <t>2017Q2</t>
+  </si>
+  <si>
+    <t>2017Q3</t>
+  </si>
+  <si>
+    <t>2017Q4</t>
+  </si>
+  <si>
+    <t>2018Q1</t>
+  </si>
+  <si>
+    <t>2018Q2</t>
+  </si>
+  <si>
+    <t>2018Q3</t>
+  </si>
+  <si>
+    <t>2018Q4</t>
+  </si>
+  <si>
+    <t>2019Q1</t>
+  </si>
+  <si>
+    <t>2019Q2</t>
+  </si>
+  <si>
+    <t>2019Q3</t>
+  </si>
+  <si>
+    <t>2019Q4</t>
+  </si>
+  <si>
+    <t>2020Q1</t>
+  </si>
+  <si>
+    <t>2020Q2</t>
+  </si>
+  <si>
+    <t>2020Q3</t>
+  </si>
+  <si>
+    <t>2020Q4</t>
+  </si>
+  <si>
+    <t>2021Q1</t>
+  </si>
+  <si>
+    <t>2021Q2</t>
+  </si>
+  <si>
+    <t>2021Q3</t>
+  </si>
+  <si>
+    <t>2021Q4</t>
+  </si>
+  <si>
+    <t>2022Q1</t>
+  </si>
+  <si>
+    <t>2022Q2</t>
+  </si>
+  <si>
+    <t>2022Q3</t>
+  </si>
+  <si>
+    <t>2022Q4</t>
+  </si>
+  <si>
+    <t>2023Q1</t>
+  </si>
+  <si>
+    <t>2023Q2</t>
+  </si>
+  <si>
+    <t>2023Q3</t>
+  </si>
+  <si>
+    <t>2023Q4</t>
+  </si>
+  <si>
+    <t>2024Q1</t>
+  </si>
+  <si>
+    <t>2024Q2</t>
+  </si>
+  <si>
+    <t>2024Q3</t>
+  </si>
+  <si>
+    <t>2024Q4</t>
   </si>
 </sst>
 </file>
@@ -684,6 +792,10 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1003,18 +1115,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DBC2ADB-9B83-4CBB-9C17-9B95D50F8DF1}">
-  <dimension ref="A1:F23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F54"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23.109375" customWidth="1"/>
-    <col min="3" max="3" width="16.109375" customWidth="1"/>
+    <col min="2" max="2" width="23.140625" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" customWidth="1"/>
     <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -1034,7 +1146,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2010</v>
       </c>
@@ -1055,7 +1167,7 @@
         <v>136634487</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2011</v>
       </c>
@@ -1075,7 +1187,7 @@
         <v>147616320</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2012</v>
       </c>
@@ -1096,7 +1208,7 @@
         <v>157630141</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2013</v>
       </c>
@@ -1117,7 +1229,7 @@
         <v>166311098</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2014</v>
       </c>
@@ -1138,7 +1250,7 @@
         <v>172725823</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2015</v>
       </c>
@@ -1159,7 +1271,7 @@
         <v>178267707</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2016</v>
       </c>
@@ -1180,7 +1292,7 @@
         <v>183403718</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2017</v>
       </c>
@@ -1201,7 +1313,7 @@
         <v>187005999</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2018</v>
       </c>
@@ -1222,7 +1334,7 @@
         <v>195032460</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2019</v>
       </c>
@@ -1243,7 +1355,7 @@
         <v>200723656</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2020</v>
       </c>
@@ -1264,7 +1376,7 @@
         <v>176752403.56140256</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2021</v>
       </c>
@@ -1285,7 +1397,7 @@
         <v>202063479</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2022</v>
       </c>
@@ -1306,7 +1418,7 @@
         <v>208744599</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2023</v>
       </c>
@@ -1327,7 +1439,7 @@
         <v>206340677</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2024</v>
       </c>
@@ -1348,17 +1460,193 @@
         <v>212497311</v>
       </c>
     </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C17" s="5"/>
     </row>
-    <row r="18" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C18" s="5"/>
     </row>
-    <row r="21" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>8</v>
+      </c>
       <c r="C21" s="4"/>
     </row>
-    <row r="23" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>10</v>
+      </c>
       <c r="C23" s="4"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>41</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
